--- a/artfynd/A 7309-2024 artfynd.xlsx
+++ b/artfynd/A 7309-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7309-2024 artfynd.xlsx
+++ b/artfynd/A 7309-2024 artfynd.xlsx
@@ -7014,11 +7014,11 @@
         <v>115468416</v>
       </c>
       <c r="B53" t="n">
-        <v>57414</v>
+        <v>57631</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7986,11 +7986,11 @@
         <v>115929707</v>
       </c>
       <c r="B61" t="n">
-        <v>57414</v>
+        <v>57631</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">

--- a/artfynd/A 7309-2024 artfynd.xlsx
+++ b/artfynd/A 7309-2024 artfynd.xlsx
@@ -6778,11 +6778,11 @@
         <v>115445838</v>
       </c>
       <c r="B51" t="n">
-        <v>56478</v>
+        <v>56688</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Långängen (Långängen), Upl</t>
+          <t>Långängen, Långängen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">

--- a/artfynd/A 7309-2024 artfynd.xlsx
+++ b/artfynd/A 7309-2024 artfynd.xlsx
@@ -6778,7 +6778,7 @@
         <v>115445838</v>
       </c>
       <c r="B51" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>115468416</v>
       </c>
       <c r="B53" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>115929707</v>
       </c>
       <c r="B61" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>

--- a/artfynd/A 7309-2024 artfynd.xlsx
+++ b/artfynd/A 7309-2024 artfynd.xlsx
@@ -6778,7 +6778,7 @@
         <v>115445838</v>
       </c>
       <c r="B51" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>

--- a/artfynd/A 7309-2024 artfynd.xlsx
+++ b/artfynd/A 7309-2024 artfynd.xlsx
@@ -6778,7 +6778,7 @@
         <v>115445838</v>
       </c>
       <c r="B51" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
